--- a/2-seances/S02-premier-contact/a-projeter/kahoot-en-ligne/import-kahoot.xlsx
+++ b/2-seances/S02-premier-contact/a-projeter/kahoot-en-ligne/import-kahoot.xlsx
@@ -6055,27 +6055,27 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Que fait la commande print en Python ?</t>
+          <t>Dans quel domaine n'y a-t-il PAS de code ?</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Elle affiche du texte à l'écran</t>
+          <t>La santé</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Elle imprime sur du papier</t>
+          <t>L'agriculture</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Elle efface le programme</t>
+          <t>La musique</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Elle calcule</t>
+          <t>Aucun : il y a du code partout</t>
         </is>
       </c>
       <c r="G9" s="14" t="n">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" s="1" t="n"/>
@@ -6112,27 +6112,27 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Combien de guillemets faut-il autour d'un texte ?</t>
+          <t>Au fond, l'ordinateur ne comprend que…</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Un seul</t>
+          <t>Le français</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Deux : un avant, un après</t>
+          <t>L'anglais</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Trois</t>
+          <t>Des 0 et des 1</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Aucun</t>
+          <t>Des images</t>
         </is>
       </c>
       <c r="G10" s="14" t="n">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" s="1" t="n"/>
@@ -6169,27 +6169,27 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Au fond, l'ordinateur ne comprend que…</t>
+          <t>Les huit élèves debout et assis, ils formaient quoi ?</t>
         </is>
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Le français</t>
+          <t>Un mot de passe</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>L'anglais</t>
+          <t>La lettre A</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Des 0 et des 1</t>
+          <t>Un numéro de téléphone</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Des images</t>
+          <t>Rien du tout</t>
         </is>
       </c>
       <c r="G11" s="14" t="n">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" s="1" t="n"/>
@@ -6226,27 +6226,27 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Quand l'ordinateur écrit en rouge, cela veut dire…</t>
+          <t>Entre Python et la machine, qui fait la traduction ?</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Il est en colère</t>
+          <t>L'interprète</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>Il t'explique ce qu'il n'a pas compris</t>
+          <t>Le clavier</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Tu es puni</t>
+          <t>Internet</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>L'ordinateur est cassé</t>
+          <t>Personne</t>
         </is>
       </c>
       <c r="G12" s="14" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" s="1" t="n"/>
@@ -6283,27 +6283,27 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Un algorithme, c'est…</t>
+          <t>Comment s'appelle le logiciel dans lequel on écrit notre code ?</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Un ordinateur très rapide</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Une suite d'ordres précis, dans le bon ordre</t>
+          <t>Thonny</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Un langage de programmation</t>
+          <t>Kahoot</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Un robot</t>
+          <t>Windows</t>
         </is>
       </c>
       <c r="G13" s="14" t="n">
@@ -6397,27 +6397,27 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Qui a écrit la première version de Facebook dans sa chambre d'étudiant ?</t>
+          <t>L'ordinateur est surtout…</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Mark Zuckerberg</t>
+          <t>Intelligent</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Elon Musk</t>
+          <t>Obéissant</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Guido van Rossum</t>
+          <t>Paresseux</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Nick D'Aloisio</t>
+          <t>Magique</t>
         </is>
       </c>
       <c r="G15" s="14" t="n">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" s="1" t="n"/>
@@ -6454,27 +6454,27 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>D'où vient le mot « bug » ?</t>
+          <t>Un algorithme, c'est…</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>D'un vrai insecte coincé dans une machine</t>
+          <t>Un ordinateur très rapide</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>D'un mot anglais qui veut dire erreur</t>
+          <t>Une suite d'ordres précis, dans le bon ordre</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Du nom d'un ordinateur</t>
+          <t>Un langage de programmation</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>D'un jeu vidéo</t>
+          <t>Un robot</t>
         </is>
       </c>
       <c r="G16" s="14" t="n">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" s="1" t="n"/>
@@ -6511,27 +6511,27 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Dans quel domaine n'y a-t-il PAS de code ?</t>
+          <t>Le robot humain de samedi dernier comprenait combien d'ordres ?</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>La santé</t>
+          <t>Un seul</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>L'agriculture</t>
+          <t>Trois</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>La musique</t>
+          <t>Dix</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Aucun : il y a du code partout</t>
+          <t>Tous les ordres</t>
         </is>
       </c>
       <c r="G17" s="14" t="n">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" s="1" t="n"/>
@@ -6568,27 +6568,27 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>L'ordinateur lit ton programme…</t>
+          <t>Une recette de cuisine, c'est…</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>De haut en bas, ligne par ligne</t>
+          <t>Un algorithme</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>De bas en haut</t>
+          <t>Un langage</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Dans le désordre</t>
+          <t>Un programme Python</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>En commençant par le milieu</t>
+          <t>Rien à voir avec le code</t>
         </is>
       </c>
       <c r="G18" s="14" t="n">
@@ -6625,27 +6625,27 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Comment s'appelle le logiciel dans lequel on écrit notre code ?</t>
+          <t>Qui a écrit la première version de Facebook dans sa chambre d'étudiant ?</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Mark Zuckerberg</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Thonny</t>
+          <t>Elon Musk</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>Kahoot</t>
+          <t>Guido van Rossum</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Windows</t>
+          <t>Nick D'Aloisio</t>
         </is>
       </c>
       <c r="G19" s="14" t="n">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" s="1" t="n"/>
@@ -6682,27 +6682,27 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Que va afficher print("Bonjour") ?</t>
+          <t>À quel âge Elon Musk a-t-il vendu son premier jeu vidéo ?</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Bonjour</t>
+          <t>8 ans</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>print Bonjour</t>
+          <t>12 ans</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>« Bonjour » avec les guillemets</t>
+          <t>20 ans</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Rien</t>
+          <t>30 ans</t>
         </is>
       </c>
       <c r="G20" s="14" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" s="1" t="n"/>
@@ -6739,27 +6739,27 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>L'ordinateur est surtout…</t>
+          <t>À 11 ans, Gitanjali Rao a inventé un appareil qui…</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Intelligent</t>
+          <t>détecte le poison dans l'eau</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>Obéissant</t>
+          <t>répare les téléphones</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
         <is>
-          <t>Paresseux</t>
+          <t>traduit les langues</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Magique</t>
+          <t>dessine des cartes</t>
         </is>
       </c>
       <c r="G21" s="14" t="n">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" s="1" t="n"/>
@@ -6796,27 +6796,27 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>À quel âge Elon Musk a-t-il vendu son premier jeu vidéo ?</t>
+          <t>Kelvin Doe, en Sierra Leone, a construit sa radio avec…</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>8 ans</t>
+          <t>des pièces neuves</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>12 ans</t>
+          <t>des déchets ramassés</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>20 ans</t>
+          <t>un kit acheté en magasin</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>30 ans</t>
+          <t>l'aide d'une grande entreprise</t>
         </is>
       </c>
       <c r="G22" s="14" t="n">
